--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Punktlighet_tog.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Punktlighet_tog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="583" documentId="8_{840FB08B-DE99-453E-B629-E89AADE1FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{718C63AD-381C-4862-9D11-CEA624D7B3CC}"/>
+  <xr:revisionPtr revIDLastSave="602" documentId="8_{840FB08B-DE99-453E-B629-E89AADE1FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFEC2FBF-66B4-4739-925F-D4A0B36CFEB1}"/>
   <bookViews>
-    <workbookView xWindow="57495" yWindow="0" windowWidth="29010" windowHeight="15585" activeTab="1" xr2:uid="{505C7C03-B5C0-43C5-A197-1F7CDBCB9E10}"/>
+    <workbookView xWindow="-30828" yWindow="936" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{505C7C03-B5C0-43C5-A197-1F7CDBCB9E10}"/>
   </bookViews>
   <sheets>
     <sheet name="Punktlighet" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Punktlighet2!$E$1:$E$649</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="40">
   <si>
     <t>År</t>
   </si>
@@ -258,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -275,6 +275,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -284,8 +285,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -29210,7 +29209,7 @@
       <c r="A747" s="4">
         <v>2025</v>
       </c>
-      <c r="B747" s="16" t="s">
+      <c r="B747" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C747" s="9">
@@ -29234,20 +29233,20 @@
       <c r="N747" s="9">
         <v>89.955022488755617</v>
       </c>
-      <c r="O747" s="15"/>
-      <c r="P747" s="15"/>
-      <c r="Q747" s="15"/>
-      <c r="R747" s="15"/>
-      <c r="S747" s="15"/>
-      <c r="T747" s="15"/>
-      <c r="U747" s="15"/>
-      <c r="V747" s="15"/>
+      <c r="O747" s="12"/>
+      <c r="P747" s="12"/>
+      <c r="Q747" s="12"/>
+      <c r="R747" s="12"/>
+      <c r="S747" s="12"/>
+      <c r="T747" s="12"/>
+      <c r="U747" s="12"/>
+      <c r="V747" s="12"/>
     </row>
     <row r="748" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A748" s="4">
         <v>2025</v>
       </c>
-      <c r="B748" s="16" t="s">
+      <c r="B748" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C748" s="9">
@@ -29279,7 +29278,7 @@
       <c r="A749" s="4">
         <v>2025</v>
       </c>
-      <c r="B749" s="16" t="s">
+      <c r="B749" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C749" s="9">
@@ -29311,7 +29310,7 @@
       <c r="A750" s="4">
         <v>2025</v>
       </c>
-      <c r="B750" s="16" t="s">
+      <c r="B750" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C750" s="9">
@@ -29343,7 +29342,7 @@
       <c r="A751" s="4">
         <v>2025</v>
       </c>
-      <c r="B751" s="16" t="s">
+      <c r="B751" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C751" s="9">
@@ -29375,7 +29374,7 @@
       <c r="A752" s="4">
         <v>2025</v>
       </c>
-      <c r="B752" s="16" t="s">
+      <c r="B752" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C752" s="9">
@@ -29407,7 +29406,7 @@
       <c r="A753" s="4">
         <v>2025</v>
       </c>
-      <c r="B753" s="16" t="s">
+      <c r="B753" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C753" s="9">
@@ -29439,7 +29438,7 @@
       <c r="A754" s="4">
         <v>2025</v>
       </c>
-      <c r="B754" s="16" t="s">
+      <c r="B754" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C754" s="9">
@@ -29468,10 +29467,10 @@
       <c r="V754" s="10"/>
     </row>
     <row r="755" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A755" s="16">
+      <c r="A755" s="4">
         <v>2026</v>
       </c>
-      <c r="B755" s="16" t="s">
+      <c r="B755" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C755" s="9">
@@ -29500,10 +29499,10 @@
       <c r="V755" s="10"/>
     </row>
     <row r="756" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A756" s="16">
+      <c r="A756" s="4">
         <v>2026</v>
       </c>
-      <c r="B756" s="16" t="s">
+      <c r="B756" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C756" s="9">
@@ -29532,10 +29531,10 @@
       <c r="V756" s="10"/>
     </row>
     <row r="757" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A757" s="16">
+      <c r="A757" s="4">
         <v>2026</v>
       </c>
-      <c r="B757" s="16" t="s">
+      <c r="B757" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C757" s="9">
@@ -29564,10 +29563,10 @@
       <c r="V757" s="10"/>
     </row>
     <row r="758" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A758" s="16">
+      <c r="A758" s="4">
         <v>2026</v>
       </c>
-      <c r="B758" s="16" t="s">
+      <c r="B758" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C758" s="9">
@@ -29596,10 +29595,10 @@
       <c r="V758" s="10"/>
     </row>
     <row r="759" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A759" s="16">
+      <c r="A759" s="4">
         <v>2026</v>
       </c>
-      <c r="B759" s="16" t="s">
+      <c r="B759" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C759" s="9">
@@ -29628,10 +29627,10 @@
       <c r="V759" s="10"/>
     </row>
     <row r="760" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A760" s="16">
+      <c r="A760" s="4">
         <v>2026</v>
       </c>
-      <c r="B760" s="16" t="s">
+      <c r="B760" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C760" s="9">
@@ -29660,10 +29659,10 @@
       <c r="V760" s="10"/>
     </row>
     <row r="761" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A761" s="16">
+      <c r="A761" s="4">
         <v>2026</v>
       </c>
-      <c r="B761" s="16" t="s">
+      <c r="B761" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C761" s="9">
@@ -29692,10 +29691,10 @@
       <c r="V761" s="10"/>
     </row>
     <row r="762" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A762" s="16">
+      <c r="A762" s="4">
         <v>2026</v>
       </c>
-      <c r="B762" s="16" t="s">
+      <c r="B762" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C762" s="9">
@@ -29724,191 +29723,334 @@
       <c r="V762" s="10"/>
     </row>
     <row r="763" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A763" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B763" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C763" s="9"/>
+      <c r="D763" s="9"/>
       <c r="R763" s="11"/>
       <c r="U763" s="9"/>
       <c r="V763" s="10"/>
     </row>
     <row r="764" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A764" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B764" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C764" s="9"/>
+      <c r="D764" s="9"/>
       <c r="R764" s="11"/>
       <c r="U764" s="9"/>
       <c r="V764" s="10"/>
     </row>
     <row r="765" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A765" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B765" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C765" s="9"/>
+      <c r="D765" s="9"/>
       <c r="R765" s="11"/>
       <c r="U765" s="9"/>
       <c r="V765" s="10"/>
     </row>
     <row r="766" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A766" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B766" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C766" s="9"/>
+      <c r="D766" s="9"/>
+      <c r="M766" s="11"/>
+      <c r="P766" s="9"/>
+      <c r="Q766" s="10"/>
       <c r="R766" s="11"/>
       <c r="U766" s="9"/>
       <c r="V766" s="10"/>
     </row>
     <row r="767" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A767" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B767" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C767" s="9"/>
+      <c r="D767" s="9"/>
+      <c r="M767" s="11"/>
+      <c r="P767" s="9"/>
+      <c r="Q767" s="10"/>
       <c r="R767" s="11"/>
       <c r="U767" s="9"/>
       <c r="V767" s="10"/>
     </row>
     <row r="768" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A768" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B768" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C768" s="9"/>
+      <c r="D768" s="9"/>
+      <c r="M768" s="11"/>
+      <c r="P768" s="9"/>
+      <c r="Q768" s="10"/>
       <c r="R768" s="11"/>
       <c r="U768" s="9"/>
       <c r="V768" s="10"/>
     </row>
-    <row r="769" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A769" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B769" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C769" s="9"/>
+      <c r="D769" s="9"/>
+      <c r="M769" s="11"/>
+      <c r="P769" s="9"/>
+      <c r="Q769" s="10"/>
       <c r="R769" s="11"/>
       <c r="U769" s="9"/>
       <c r="V769" s="10"/>
     </row>
-    <row r="770" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A770" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B770" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C770" s="9"/>
+      <c r="D770" s="9"/>
+      <c r="M770" s="11"/>
+      <c r="P770" s="9"/>
+      <c r="Q770" s="10"/>
       <c r="R770" s="11"/>
       <c r="U770" s="9"/>
       <c r="V770" s="10"/>
     </row>
-    <row r="771" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D771" s="9"/>
+      <c r="M771" s="11"/>
+      <c r="P771" s="9"/>
+      <c r="Q771" s="10"/>
       <c r="R771" s="11"/>
       <c r="U771" s="9"/>
       <c r="V771" s="10"/>
     </row>
-    <row r="772" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M772" s="11"/>
+      <c r="P772" s="9"/>
+      <c r="Q772" s="10"/>
       <c r="R772" s="11"/>
       <c r="U772" s="9"/>
       <c r="V772" s="10"/>
     </row>
-    <row r="773" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M773" s="11"/>
+      <c r="P773" s="9"/>
+      <c r="Q773" s="10"/>
       <c r="R773" s="11"/>
       <c r="U773" s="9"/>
       <c r="V773" s="10"/>
     </row>
-    <row r="774" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M774" s="11"/>
+      <c r="P774" s="9"/>
+      <c r="Q774" s="10"/>
       <c r="R774" s="11"/>
       <c r="U774" s="9"/>
       <c r="V774" s="10"/>
     </row>
-    <row r="775" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M775" s="11"/>
+      <c r="P775" s="9"/>
+      <c r="Q775" s="10"/>
       <c r="R775" s="11"/>
       <c r="U775" s="9"/>
       <c r="V775" s="10"/>
     </row>
-    <row r="776" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M776" s="11"/>
+      <c r="P776" s="9"/>
+      <c r="Q776" s="10"/>
       <c r="R776" s="11"/>
       <c r="U776" s="9"/>
       <c r="V776" s="10"/>
     </row>
-    <row r="777" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M777" s="11"/>
+      <c r="P777" s="9"/>
+      <c r="Q777" s="10"/>
       <c r="R777" s="11"/>
       <c r="U777" s="9"/>
       <c r="V777" s="10"/>
     </row>
-    <row r="778" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M778" s="11"/>
+      <c r="P778" s="9"/>
+      <c r="Q778" s="10"/>
       <c r="R778" s="11"/>
       <c r="U778" s="9"/>
       <c r="V778" s="10"/>
     </row>
-    <row r="779" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M779" s="11"/>
+      <c r="P779" s="9"/>
+      <c r="Q779" s="10"/>
       <c r="R779" s="11"/>
       <c r="U779" s="9"/>
       <c r="V779" s="10"/>
     </row>
-    <row r="780" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M780" s="11"/>
+      <c r="P780" s="9"/>
+      <c r="Q780" s="10"/>
       <c r="R780" s="11"/>
       <c r="U780" s="9"/>
       <c r="V780" s="10"/>
     </row>
-    <row r="781" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M781" s="11"/>
+      <c r="P781" s="9"/>
+      <c r="Q781" s="10"/>
       <c r="R781" s="11"/>
       <c r="U781" s="9"/>
       <c r="V781" s="10"/>
     </row>
-    <row r="782" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M782" s="11"/>
+      <c r="P782" s="9"/>
+      <c r="Q782" s="10"/>
       <c r="R782" s="11"/>
       <c r="U782" s="9"/>
       <c r="V782" s="10"/>
     </row>
-    <row r="783" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M783" s="11"/>
+      <c r="P783" s="9"/>
+      <c r="Q783" s="10"/>
       <c r="R783" s="11"/>
       <c r="U783" s="9"/>
       <c r="V783" s="10"/>
     </row>
-    <row r="784" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:22" x14ac:dyDescent="0.25">
       <c r="R784" s="11"/>
       <c r="U784" s="9"/>
       <c r="V784" s="10"/>
     </row>
-    <row r="785" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="785" spans="6:22" x14ac:dyDescent="0.25">
       <c r="R785" s="11"/>
       <c r="U785" s="9"/>
       <c r="V785" s="10"/>
     </row>
-    <row r="786" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="786" spans="6:22" x14ac:dyDescent="0.25">
       <c r="R786" s="11"/>
       <c r="U786" s="9"/>
       <c r="V786" s="10"/>
     </row>
-    <row r="787" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="787" spans="6:22" x14ac:dyDescent="0.25">
+      <c r="F787" s="11"/>
+      <c r="I787" s="9"/>
+      <c r="J787" s="10"/>
       <c r="R787" s="11"/>
       <c r="U787" s="9"/>
       <c r="V787" s="10"/>
     </row>
-    <row r="788" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="788" spans="6:22" x14ac:dyDescent="0.25">
+      <c r="F788" s="11"/>
+      <c r="I788" s="9"/>
+      <c r="J788" s="10"/>
       <c r="R788" s="11"/>
       <c r="U788" s="9"/>
       <c r="V788" s="10"/>
     </row>
-    <row r="789" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="789" spans="6:22" x14ac:dyDescent="0.25">
+      <c r="F789" s="11"/>
+      <c r="I789" s="9"/>
+      <c r="J789" s="10"/>
       <c r="R789" s="11"/>
       <c r="U789" s="9"/>
       <c r="V789" s="10"/>
     </row>
-    <row r="790" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="790" spans="6:22" x14ac:dyDescent="0.25">
+      <c r="F790" s="11"/>
+      <c r="I790" s="9"/>
+      <c r="J790" s="10"/>
       <c r="R790" s="11"/>
       <c r="U790" s="9"/>
       <c r="V790" s="10"/>
     </row>
-    <row r="791" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="791" spans="6:22" x14ac:dyDescent="0.25">
+      <c r="F791" s="11"/>
+      <c r="I791" s="9"/>
+      <c r="J791" s="10"/>
       <c r="R791" s="11"/>
       <c r="U791" s="9"/>
       <c r="V791" s="10"/>
     </row>
-    <row r="792" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="792" spans="6:22" x14ac:dyDescent="0.25">
+      <c r="F792" s="11"/>
+      <c r="I792" s="9"/>
+      <c r="J792" s="10"/>
       <c r="R792" s="11"/>
       <c r="U792" s="9"/>
       <c r="V792" s="10"/>
     </row>
-    <row r="793" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="793" spans="6:22" x14ac:dyDescent="0.25">
+      <c r="F793" s="11"/>
+      <c r="I793" s="9"/>
+      <c r="J793" s="10"/>
       <c r="R793" s="11"/>
       <c r="U793" s="9"/>
       <c r="V793" s="10"/>
     </row>
-    <row r="794" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="794" spans="6:22" x14ac:dyDescent="0.25">
+      <c r="F794" s="11"/>
+      <c r="I794" s="9"/>
+      <c r="J794" s="10"/>
       <c r="R794" s="11"/>
       <c r="U794" s="9"/>
       <c r="V794" s="10"/>
     </row>
-    <row r="795" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="795" spans="6:22" x14ac:dyDescent="0.25">
       <c r="R795" s="11"/>
       <c r="U795" s="9"/>
       <c r="V795" s="10"/>
     </row>
-    <row r="796" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="796" spans="6:22" x14ac:dyDescent="0.25">
       <c r="R796" s="11"/>
       <c r="U796" s="9"/>
       <c r="V796" s="10"/>
     </row>
-    <row r="797" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="797" spans="6:22" x14ac:dyDescent="0.25">
       <c r="R797" s="11"/>
       <c r="U797" s="9"/>
       <c r="V797" s="10"/>
     </row>
-    <row r="798" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="798" spans="6:22" x14ac:dyDescent="0.25">
       <c r="R798" s="11"/>
       <c r="U798" s="9"/>
       <c r="V798" s="10"/>
     </row>
-    <row r="799" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="799" spans="6:22" x14ac:dyDescent="0.25">
       <c r="R799" s="11"/>
       <c r="U799" s="9"/>
       <c r="V799" s="10"/>
     </row>
-    <row r="800" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="800" spans="6:22" x14ac:dyDescent="0.25">
       <c r="R800" s="11"/>
       <c r="U800" s="9"/>
       <c r="V800" s="10"/>
@@ -30048,45 +30190,45 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12" t="s">
+      <c r="D2" s="13"/>
+      <c r="E2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12" t="s">
+      <c r="F2" s="13"/>
+      <c r="G2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12" t="s">
+      <c r="H2" s="13"/>
+      <c r="I2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12" t="s">
+      <c r="L2" s="13"/>
+      <c r="M2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12" t="s">
+      <c r="N2" s="13"/>
+      <c r="O2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12" t="s">
+      <c r="R2" s="13"/>
+      <c r="S2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="12"/>
+      <c r="T2" s="13"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="13">
         <v>2019</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -30148,7 +30290,7 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
@@ -30208,7 +30350,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
@@ -30268,7 +30410,7 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
@@ -30328,7 +30470,7 @@
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
@@ -30388,7 +30530,7 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
@@ -30448,7 +30590,7 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
@@ -30508,7 +30650,7 @@
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
@@ -30568,7 +30710,7 @@
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
@@ -30628,7 +30770,7 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
@@ -30688,7 +30830,7 @@
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
@@ -30748,7 +30890,7 @@
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
+      <c r="A14" s="13"/>
       <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
@@ -30808,7 +30950,7 @@
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+      <c r="A15" s="13">
         <v>2020</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -30870,7 +31012,7 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
@@ -30930,7 +31072,7 @@
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
+      <c r="A17" s="13"/>
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
@@ -30990,7 +31132,7 @@
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
+      <c r="A18" s="13"/>
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
@@ -31050,7 +31192,7 @@
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
+      <c r="A19" s="13"/>
       <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
@@ -31110,7 +31252,7 @@
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
+      <c r="A20" s="13"/>
       <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
@@ -31170,7 +31312,7 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
+      <c r="A21" s="13"/>
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
@@ -31230,7 +31372,7 @@
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
+      <c r="A22" s="13"/>
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
@@ -31290,7 +31432,7 @@
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
+      <c r="A23" s="13"/>
       <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
@@ -31350,7 +31492,7 @@
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
+      <c r="A24" s="13"/>
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
@@ -31410,7 +31552,7 @@
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
+      <c r="A25" s="13"/>
       <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
@@ -31470,7 +31612,7 @@
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
+      <c r="A26" s="13"/>
       <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
@@ -31530,7 +31672,7 @@
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
+      <c r="A27" s="13">
         <v>2021</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -31592,7 +31734,7 @@
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="12"/>
+      <c r="A28" s="13"/>
       <c r="B28" s="1" t="s">
         <v>14</v>
       </c>
@@ -31652,7 +31794,7 @@
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
+      <c r="A29" s="13"/>
       <c r="B29" s="1" t="s">
         <v>15</v>
       </c>
@@ -31712,7 +31854,7 @@
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
+      <c r="A30" s="13"/>
       <c r="B30" s="1" t="s">
         <v>16</v>
       </c>
@@ -31772,7 +31914,7 @@
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
+      <c r="A31" s="13"/>
       <c r="B31" s="1" t="s">
         <v>17</v>
       </c>
@@ -31832,7 +31974,7 @@
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="12"/>
+      <c r="A32" s="13"/>
       <c r="B32" s="1" t="s">
         <v>18</v>
       </c>
@@ -31892,7 +32034,7 @@
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
+      <c r="A33" s="13"/>
       <c r="B33" s="1" t="s">
         <v>19</v>
       </c>
@@ -31952,7 +32094,7 @@
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A34" s="12"/>
+      <c r="A34" s="13"/>
       <c r="B34" s="1" t="s">
         <v>20</v>
       </c>
@@ -32012,7 +32154,7 @@
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
+      <c r="A35" s="13"/>
       <c r="B35" s="1" t="s">
         <v>21</v>
       </c>
@@ -32072,7 +32214,7 @@
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
+      <c r="A36" s="13"/>
       <c r="B36" s="1" t="s">
         <v>22</v>
       </c>
@@ -32132,7 +32274,7 @@
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
+      <c r="A37" s="13"/>
       <c r="B37" s="1" t="s">
         <v>23</v>
       </c>
@@ -32192,7 +32334,7 @@
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
+      <c r="A38" s="13"/>
       <c r="B38" s="1" t="s">
         <v>24</v>
       </c>
@@ -32252,7 +32394,7 @@
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A39" s="12">
+      <c r="A39" s="13">
         <v>2022</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -32314,7 +32456,7 @@
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
+      <c r="A40" s="13"/>
       <c r="B40" s="1" t="s">
         <v>14</v>
       </c>
@@ -32374,7 +32516,7 @@
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
+      <c r="A41" s="13"/>
       <c r="B41" s="1" t="s">
         <v>15</v>
       </c>
@@ -32434,7 +32576,7 @@
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
+      <c r="A42" s="13"/>
       <c r="B42" s="1" t="s">
         <v>16</v>
       </c>
@@ -32494,7 +32636,7 @@
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
+      <c r="A43" s="13"/>
       <c r="B43" s="1" t="s">
         <v>17</v>
       </c>
@@ -32554,7 +32696,7 @@
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
+      <c r="A44" s="13"/>
       <c r="B44" s="1" t="s">
         <v>18</v>
       </c>
@@ -32614,7 +32756,7 @@
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
+      <c r="A45" s="13"/>
       <c r="B45" s="1" t="s">
         <v>19</v>
       </c>
@@ -32674,7 +32816,7 @@
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
+      <c r="A46" s="13"/>
       <c r="B46" s="1" t="s">
         <v>20</v>
       </c>
@@ -32734,7 +32876,7 @@
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
+      <c r="A47" s="13"/>
       <c r="B47" s="1" t="s">
         <v>21</v>
       </c>
@@ -32794,7 +32936,7 @@
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
+      <c r="A48" s="13"/>
       <c r="B48" s="1" t="s">
         <v>22</v>
       </c>
@@ -32854,7 +32996,7 @@
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
+      <c r="A49" s="13"/>
       <c r="B49" s="1" t="s">
         <v>23</v>
       </c>
@@ -32914,7 +33056,7 @@
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
+      <c r="A50" s="13"/>
       <c r="B50" s="1" t="s">
         <v>24</v>
       </c>
@@ -32974,7 +33116,7 @@
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A51" s="12">
+      <c r="A51" s="13">
         <v>2023</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -33036,7 +33178,7 @@
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
+      <c r="A52" s="13"/>
       <c r="B52" s="1" t="s">
         <v>14</v>
       </c>
@@ -33096,7 +33238,7 @@
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+      <c r="A53" s="13"/>
       <c r="B53" s="1" t="s">
         <v>15</v>
       </c>
@@ -33156,7 +33298,7 @@
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
+      <c r="A54" s="13"/>
       <c r="B54" s="1" t="s">
         <v>16</v>
       </c>
@@ -33216,7 +33358,7 @@
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
+      <c r="A55" s="13"/>
       <c r="B55" s="1" t="s">
         <v>17</v>
       </c>
@@ -33276,7 +33418,7 @@
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
+      <c r="A56" s="13"/>
       <c r="B56" s="1" t="s">
         <v>18</v>
       </c>
@@ -33336,7 +33478,7 @@
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
+      <c r="A57" s="13"/>
       <c r="B57" s="1" t="s">
         <v>19</v>
       </c>
@@ -33396,7 +33538,7 @@
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
+      <c r="A58" s="13"/>
       <c r="B58" s="1" t="s">
         <v>20</v>
       </c>
@@ -33456,7 +33598,7 @@
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
+      <c r="A59" s="13"/>
       <c r="B59" s="1" t="s">
         <v>21</v>
       </c>
@@ -33516,7 +33658,7 @@
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
+      <c r="A60" s="13"/>
       <c r="B60" s="1" t="s">
         <v>22</v>
       </c>
@@ -33576,7 +33718,7 @@
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
+      <c r="A61" s="13"/>
       <c r="B61" s="1" t="s">
         <v>23</v>
       </c>
@@ -33636,7 +33778,7 @@
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
+      <c r="A62" s="13"/>
       <c r="B62" s="1" t="s">
         <v>24</v>
       </c>
@@ -33696,7 +33838,7 @@
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A63" s="13">
+      <c r="A63" s="14">
         <v>2024</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -33758,7 +33900,7 @@
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A64" s="14"/>
+      <c r="A64" s="15"/>
       <c r="B64" s="1" t="s">
         <v>14</v>
       </c>
@@ -33818,7 +33960,7 @@
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65" s="14"/>
+      <c r="A65" s="15"/>
       <c r="B65" s="1" t="s">
         <v>15</v>
       </c>
@@ -33878,7 +34020,7 @@
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A66" s="14"/>
+      <c r="A66" s="15"/>
       <c r="B66" s="1" t="s">
         <v>16</v>
       </c>
@@ -33938,7 +34080,7 @@
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="14"/>
+      <c r="A67" s="15"/>
       <c r="B67" s="1" t="s">
         <v>17</v>
       </c>
@@ -33998,7 +34140,7 @@
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A68" s="14"/>
+      <c r="A68" s="15"/>
       <c r="B68" s="1" t="s">
         <v>18</v>
       </c>
@@ -34058,7 +34200,7 @@
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A69" s="14"/>
+      <c r="A69" s="15"/>
       <c r="B69" s="1" t="s">
         <v>19</v>
       </c>
@@ -34118,7 +34260,7 @@
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A70" s="14"/>
+      <c r="A70" s="15"/>
       <c r="B70" s="1" t="s">
         <v>20</v>
       </c>
@@ -34178,7 +34320,7 @@
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A71" s="14"/>
+      <c r="A71" s="15"/>
       <c r="B71" s="1" t="s">
         <v>21</v>
       </c>
@@ -34238,7 +34380,7 @@
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="14"/>
+      <c r="A72" s="15"/>
       <c r="B72" s="1" t="s">
         <v>22</v>
       </c>
@@ -34298,7 +34440,7 @@
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A73" s="14"/>
+      <c r="A73" s="15"/>
       <c r="B73" s="1" t="s">
         <v>23</v>
       </c>
@@ -34358,7 +34500,7 @@
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A74" s="14"/>
+      <c r="A74" s="15"/>
       <c r="B74" s="4" t="s">
         <v>24</v>
       </c>
@@ -34507,17 +34649,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="304c15a9-2ddf-417f-8912-8cf6a1609eab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -34526,7 +34657,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001F0BB1C88B026E498516C75AD9D26285" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5fb15fa5fb8ec6c836b9d7d5a959bb8a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="304c15a9-2ddf-417f-8912-8cf6a1609eab" xmlns:ns3="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9ddd68b27bb9e6f16d84f1577050cb1c" ns2:_="" ns3:_="">
     <xsd:import namespace="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
@@ -34781,18 +34912,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11171811-4752-42CE-913B-A1196C5C2AA8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
-    <ds:schemaRef ds:uri="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="304c15a9-2ddf-417f-8912-8cf6a1609eab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7B921E6-00DE-4D0E-B400-431DDE188271}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -34800,7 +34931,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BAB492D-29AE-4FBB-B174-1C81B2D3C817}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34817,4 +34948,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11171811-4752-42CE-913B-A1196C5C2AA8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
+    <ds:schemaRef ds:uri="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Punktlighet_tog.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Punktlighet_tog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="602" documentId="8_{840FB08B-DE99-453E-B629-E89AADE1FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFEC2FBF-66B4-4739-925F-D4A0B36CFEB1}"/>
+  <xr:revisionPtr revIDLastSave="667" documentId="8_{840FB08B-DE99-453E-B629-E89AADE1FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{944B3435-B6DB-4EDB-831E-C3069AC3F9D1}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="936" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{505C7C03-B5C0-43C5-A197-1F7CDBCB9E10}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="57840" windowHeight="15720" activeTab="1" xr2:uid="{505C7C03-B5C0-43C5-A197-1F7CDBCB9E10}"/>
   </bookViews>
   <sheets>
     <sheet name="Punktlighet" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Punktlighet2!$E$1:$E$649</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="41">
   <si>
     <t>År</t>
   </si>
@@ -162,6 +162,9 @@
   <si>
     <t>ju</t>
   </si>
+  <si>
+    <t>Sem</t>
+  </si>
 </sst>
 </file>
 
@@ -258,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -285,6 +288,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5175,7 +5179,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DB8626-0F1C-45B1-B742-083DABC571E5}">
-  <dimension ref="A1:AJ811"/>
+  <dimension ref="A1:AJ882"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="16.140625" customWidth="1"/>
@@ -29729,8 +29733,27 @@
       <c r="B763" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C763" s="9"/>
-      <c r="D763" s="9"/>
+      <c r="C763" s="9">
+        <v>88.121990369181376</v>
+      </c>
+      <c r="D763" s="9">
+        <v>65.865384615384613</v>
+      </c>
+      <c r="E763" t="s">
+        <v>4</v>
+      </c>
+      <c r="F763" s="10">
+        <v>623</v>
+      </c>
+      <c r="G763" s="10">
+        <v>624</v>
+      </c>
+      <c r="M763" s="9">
+        <v>88.121990369181376</v>
+      </c>
+      <c r="N763" s="9">
+        <v>65.865384615384613</v>
+      </c>
       <c r="R763" s="11"/>
       <c r="U763" s="9"/>
       <c r="V763" s="10"/>
@@ -29742,8 +29765,27 @@
       <c r="B764" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C764" s="9"/>
-      <c r="D764" s="9"/>
+      <c r="C764" s="9">
+        <v>80.314960629921259</v>
+      </c>
+      <c r="D764" s="9">
+        <v>59.519999999999996</v>
+      </c>
+      <c r="E764" t="s">
+        <v>5</v>
+      </c>
+      <c r="F764" s="10">
+        <v>635</v>
+      </c>
+      <c r="G764" s="10">
+        <v>626</v>
+      </c>
+      <c r="M764" s="9">
+        <v>80.314960629921259</v>
+      </c>
+      <c r="N764" s="9">
+        <v>59.519999999999996</v>
+      </c>
       <c r="R764" s="11"/>
       <c r="U764" s="9"/>
       <c r="V764" s="10"/>
@@ -29755,8 +29797,27 @@
       <c r="B765" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C765" s="9"/>
-      <c r="D765" s="9"/>
+      <c r="C765" s="9">
+        <v>79.40251572327044</v>
+      </c>
+      <c r="D765" s="9">
+        <v>69.16932907348243</v>
+      </c>
+      <c r="E765" t="s">
+        <v>6</v>
+      </c>
+      <c r="F765" s="10">
+        <v>636</v>
+      </c>
+      <c r="G765" s="10">
+        <v>629</v>
+      </c>
+      <c r="M765" s="9">
+        <v>79.40251572327044</v>
+      </c>
+      <c r="N765" s="9">
+        <v>69.16932907348243</v>
+      </c>
       <c r="R765" s="11"/>
       <c r="U765" s="9"/>
       <c r="V765" s="10"/>
@@ -29768,9 +29829,27 @@
       <c r="B766" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C766" s="9"/>
-      <c r="D766" s="9"/>
-      <c r="M766" s="11"/>
+      <c r="C766" s="9">
+        <v>79.379844961240309</v>
+      </c>
+      <c r="D766" s="9">
+        <v>80</v>
+      </c>
+      <c r="E766" t="s">
+        <v>7</v>
+      </c>
+      <c r="F766" s="10">
+        <v>646</v>
+      </c>
+      <c r="G766" s="10">
+        <v>639</v>
+      </c>
+      <c r="M766" s="9">
+        <v>79.379844961240309</v>
+      </c>
+      <c r="N766" s="9">
+        <v>80</v>
+      </c>
       <c r="P766" s="9"/>
       <c r="Q766" s="10"/>
       <c r="R766" s="11"/>
@@ -29784,9 +29863,27 @@
       <c r="B767" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C767" s="9"/>
-      <c r="D767" s="9"/>
-      <c r="M767" s="11"/>
+      <c r="C767" s="9">
+        <v>73.36448598130842</v>
+      </c>
+      <c r="D767" s="9">
+        <v>65.463108320251166</v>
+      </c>
+      <c r="E767" t="s">
+        <v>8</v>
+      </c>
+      <c r="F767" s="10">
+        <v>643</v>
+      </c>
+      <c r="G767" s="10">
+        <v>637</v>
+      </c>
+      <c r="M767" s="9">
+        <v>73.36448598130842</v>
+      </c>
+      <c r="N767" s="9">
+        <v>65.463108320251166</v>
+      </c>
       <c r="P767" s="9"/>
       <c r="Q767" s="10"/>
       <c r="R767" s="11"/>
@@ -29800,315 +29897,1944 @@
       <c r="B768" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C768" s="9"/>
-      <c r="D768" s="9"/>
-      <c r="M768" s="11"/>
+      <c r="C768" s="9">
+        <v>70.962732919254663</v>
+      </c>
+      <c r="D768" s="9">
+        <v>70.329670329670321</v>
+      </c>
+      <c r="E768" t="s">
+        <v>40</v>
+      </c>
+      <c r="F768" s="10">
+        <v>644</v>
+      </c>
+      <c r="G768" s="10">
+        <v>637</v>
+      </c>
+      <c r="M768" s="9">
+        <v>70.962732919254663</v>
+      </c>
+      <c r="N768" s="9">
+        <v>70.329670329670321</v>
+      </c>
       <c r="P768" s="9"/>
       <c r="Q768" s="10"/>
       <c r="R768" s="11"/>
       <c r="U768" s="9"/>
       <c r="V768" s="10"/>
     </row>
-    <row r="769" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A769" s="4">
         <v>2026</v>
       </c>
       <c r="B769" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C769" s="9"/>
-      <c r="D769" s="9"/>
-      <c r="M769" s="11"/>
+      <c r="C769" s="9">
+        <v>100</v>
+      </c>
+      <c r="D769" s="9">
+        <v>74.015748031496059</v>
+      </c>
+      <c r="E769" t="s">
+        <v>9</v>
+      </c>
+      <c r="F769" s="10">
+        <v>645</v>
+      </c>
+      <c r="G769" s="10">
+        <v>640</v>
+      </c>
+      <c r="K769" s="9"/>
+      <c r="M769" s="9">
+        <v>100</v>
+      </c>
+      <c r="N769" s="9">
+        <v>74.015748031496059</v>
+      </c>
       <c r="P769" s="9"/>
       <c r="Q769" s="10"/>
       <c r="R769" s="11"/>
       <c r="U769" s="9"/>
       <c r="V769" s="10"/>
     </row>
-    <row r="770" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A770" s="4">
         <v>2026</v>
       </c>
       <c r="B770" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C770" s="9"/>
-      <c r="D770" s="9"/>
-      <c r="M770" s="11"/>
+      <c r="C770" s="9">
+        <v>78.773584905660371</v>
+      </c>
+      <c r="D770" s="9">
+        <v>68.012924071082395</v>
+      </c>
+      <c r="E770" t="s">
+        <v>10</v>
+      </c>
+      <c r="F770" s="10">
+        <v>636</v>
+      </c>
+      <c r="G770" s="10">
+        <v>620</v>
+      </c>
+      <c r="K770" s="9"/>
+      <c r="M770" s="9">
+        <v>78.773584905660371</v>
+      </c>
+      <c r="N770" s="9">
+        <v>68.012924071082395</v>
+      </c>
       <c r="P770" s="9"/>
       <c r="Q770" s="10"/>
       <c r="R770" s="11"/>
       <c r="U770" s="9"/>
       <c r="V770" s="10"/>
     </row>
-    <row r="771" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D771" s="9"/>
-      <c r="M771" s="11"/>
+    <row r="771" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A771" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B771" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C771" s="9">
+        <v>72.955974842767304</v>
+      </c>
+      <c r="D771" s="9">
+        <v>77.258064516129039</v>
+      </c>
+      <c r="E771" t="s">
+        <v>11</v>
+      </c>
+      <c r="F771" s="10">
+        <v>636</v>
+      </c>
+      <c r="G771" s="10">
+        <v>620</v>
+      </c>
+      <c r="K771" s="9"/>
+      <c r="M771" s="9">
+        <v>72.955974842767304</v>
+      </c>
+      <c r="N771" s="9">
+        <v>77.258064516129039</v>
+      </c>
       <c r="P771" s="9"/>
       <c r="Q771" s="10"/>
       <c r="R771" s="11"/>
       <c r="U771" s="9"/>
       <c r="V771" s="10"/>
     </row>
-    <row r="772" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M772" s="11"/>
+    <row r="772" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A772" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B772" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C772" s="9">
+        <v>87.451737451737458</v>
+      </c>
+      <c r="D772" s="9">
+        <v>51.587301587301582</v>
+      </c>
+      <c r="E772" t="s">
+        <v>4</v>
+      </c>
+      <c r="F772" s="10">
+        <v>518</v>
+      </c>
+      <c r="G772" s="10">
+        <v>504</v>
+      </c>
+      <c r="K772" s="9"/>
+      <c r="M772" s="9">
+        <v>87.451737451737458</v>
+      </c>
+      <c r="N772" s="9">
+        <v>51.587301587301582</v>
+      </c>
       <c r="P772" s="9"/>
       <c r="Q772" s="10"/>
       <c r="R772" s="11"/>
       <c r="U772" s="9"/>
       <c r="V772" s="10"/>
     </row>
-    <row r="773" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M773" s="11"/>
+    <row r="773" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A773" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B773" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C773" s="9">
+        <v>100</v>
+      </c>
+      <c r="D773" s="9">
+        <v>54.043392504930964</v>
+      </c>
+      <c r="E773" t="s">
+        <v>5</v>
+      </c>
+      <c r="F773" s="10">
+        <v>558</v>
+      </c>
+      <c r="G773" s="10">
+        <v>548</v>
+      </c>
+      <c r="K773" s="9"/>
+      <c r="M773" s="9">
+        <v>100</v>
+      </c>
+      <c r="N773" s="9">
+        <v>54.043392504930964</v>
+      </c>
       <c r="P773" s="9"/>
       <c r="Q773" s="10"/>
       <c r="R773" s="11"/>
       <c r="U773" s="9"/>
       <c r="V773" s="10"/>
     </row>
-    <row r="774" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M774" s="11"/>
+    <row r="774" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A774" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B774" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C774" s="9">
+        <v>75.666074600355245</v>
+      </c>
+      <c r="D774" s="9">
+        <v>64.051094890510953</v>
+      </c>
+      <c r="E774" t="s">
+        <v>6</v>
+      </c>
+      <c r="F774" s="10">
+        <v>563</v>
+      </c>
+      <c r="G774" s="10">
+        <v>554</v>
+      </c>
+      <c r="K774" s="9"/>
+      <c r="M774" s="9">
+        <v>75.666074600355245</v>
+      </c>
+      <c r="N774" s="9">
+        <v>64.051094890510953</v>
+      </c>
       <c r="P774" s="9"/>
       <c r="Q774" s="10"/>
       <c r="R774" s="11"/>
       <c r="U774" s="9"/>
       <c r="V774" s="10"/>
     </row>
-    <row r="775" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M775" s="11"/>
-      <c r="P775" s="9"/>
-      <c r="Q775" s="10"/>
-      <c r="R775" s="11"/>
-      <c r="U775" s="9"/>
-      <c r="V775" s="10"/>
-    </row>
-    <row r="776" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M776" s="11"/>
-      <c r="P776" s="9"/>
-      <c r="Q776" s="10"/>
-      <c r="R776" s="11"/>
-      <c r="U776" s="9"/>
-      <c r="V776" s="10"/>
-    </row>
-    <row r="777" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M777" s="11"/>
-      <c r="P777" s="9"/>
-      <c r="Q777" s="10"/>
-      <c r="R777" s="11"/>
-      <c r="U777" s="9"/>
-      <c r="V777" s="10"/>
-    </row>
-    <row r="778" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M778" s="11"/>
-      <c r="P778" s="9"/>
-      <c r="Q778" s="10"/>
-      <c r="R778" s="11"/>
-      <c r="U778" s="9"/>
-      <c r="V778" s="10"/>
-    </row>
-    <row r="779" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M779" s="11"/>
-      <c r="P779" s="9"/>
-      <c r="Q779" s="10"/>
-      <c r="R779" s="11"/>
-      <c r="U779" s="9"/>
-      <c r="V779" s="10"/>
-    </row>
-    <row r="780" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M780" s="11"/>
-      <c r="P780" s="9"/>
-      <c r="Q780" s="10"/>
-      <c r="R780" s="11"/>
-      <c r="U780" s="9"/>
-      <c r="V780" s="10"/>
-    </row>
-    <row r="781" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M781" s="11"/>
-      <c r="P781" s="9"/>
-      <c r="Q781" s="10"/>
-      <c r="R781" s="11"/>
-      <c r="U781" s="9"/>
-      <c r="V781" s="10"/>
-    </row>
-    <row r="782" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M782" s="11"/>
-      <c r="P782" s="9"/>
-      <c r="Q782" s="10"/>
-      <c r="R782" s="11"/>
-      <c r="U782" s="9"/>
-      <c r="V782" s="10"/>
-    </row>
-    <row r="783" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M783" s="11"/>
-      <c r="P783" s="9"/>
-      <c r="Q783" s="10"/>
-      <c r="R783" s="11"/>
-      <c r="U783" s="9"/>
-      <c r="V783" s="10"/>
-    </row>
-    <row r="784" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R784" s="11"/>
-      <c r="U784" s="9"/>
-      <c r="V784" s="10"/>
-    </row>
-    <row r="785" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="R785" s="11"/>
-      <c r="U785" s="9"/>
-      <c r="V785" s="10"/>
-    </row>
-    <row r="786" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="R786" s="11"/>
-      <c r="U786" s="9"/>
-      <c r="V786" s="10"/>
-    </row>
-    <row r="787" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F787" s="11"/>
+    <row r="775" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A775" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B775" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C775" s="9">
+        <v>75.088967971530252</v>
+      </c>
+      <c r="D775" s="9">
+        <v>59.132007233273058</v>
+      </c>
+      <c r="E775" t="s">
+        <v>7</v>
+      </c>
+      <c r="F775" s="10">
+        <v>564</v>
+      </c>
+      <c r="G775" s="10">
+        <v>554</v>
+      </c>
+      <c r="K775" s="9"/>
+      <c r="M775" s="9">
+        <v>75.088967971530252</v>
+      </c>
+      <c r="N775" s="9">
+        <v>59.132007233273058</v>
+      </c>
+      <c r="S775" s="11"/>
+      <c r="V775" s="9"/>
+      <c r="W775" s="10"/>
+    </row>
+    <row r="776" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A776" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B776" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C776" s="9">
+        <v>63.879003558718864</v>
+      </c>
+      <c r="D776" s="9">
+        <v>62.613430127041745</v>
+      </c>
+      <c r="E776" t="s">
+        <v>8</v>
+      </c>
+      <c r="F776" s="10">
+        <v>564</v>
+      </c>
+      <c r="G776" s="10">
+        <v>556</v>
+      </c>
+      <c r="K776" s="9"/>
+      <c r="M776" s="9">
+        <v>63.879003558718864</v>
+      </c>
+      <c r="N776" s="9">
+        <v>62.613430127041745</v>
+      </c>
+      <c r="S776" s="11"/>
+      <c r="V776" s="9"/>
+      <c r="W776" s="10"/>
+    </row>
+    <row r="777" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A777" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B777" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C777" s="9">
+        <v>64.52762923351159</v>
+      </c>
+      <c r="D777" s="9">
+        <v>67.753623188405797</v>
+      </c>
+      <c r="E777" t="s">
+        <v>40</v>
+      </c>
+      <c r="F777" s="10">
+        <v>561</v>
+      </c>
+      <c r="G777" s="10">
+        <v>552</v>
+      </c>
+      <c r="K777" s="9"/>
+      <c r="M777" s="9">
+        <v>64.52762923351159</v>
+      </c>
+      <c r="N777" s="9">
+        <v>67.753623188405797</v>
+      </c>
+      <c r="S777" s="11"/>
+      <c r="V777" s="9"/>
+      <c r="W777" s="10"/>
+    </row>
+    <row r="778" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A778" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B778" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C778" s="9">
+        <v>73.451327433628322</v>
+      </c>
+      <c r="D778" s="9">
+        <v>76.727272727272734</v>
+      </c>
+      <c r="E778" t="s">
+        <v>9</v>
+      </c>
+      <c r="F778" s="10">
+        <v>565</v>
+      </c>
+      <c r="G778" s="10">
+        <v>554</v>
+      </c>
+      <c r="K778" s="9"/>
+      <c r="M778" s="9">
+        <v>73.451327433628322</v>
+      </c>
+      <c r="N778" s="9">
+        <v>76.727272727272734</v>
+      </c>
+      <c r="S778" s="11"/>
+      <c r="V778" s="9"/>
+      <c r="W778" s="10"/>
+    </row>
+    <row r="779" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A779" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B779" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C779" s="9">
+        <v>75.80071174377224</v>
+      </c>
+      <c r="D779" s="9">
+        <v>67.542213883677292</v>
+      </c>
+      <c r="E779" t="s">
+        <v>10</v>
+      </c>
+      <c r="F779" s="10">
+        <v>562</v>
+      </c>
+      <c r="G779" s="10">
+        <v>535</v>
+      </c>
+      <c r="K779" s="9"/>
+      <c r="M779" s="9">
+        <v>75.80071174377224</v>
+      </c>
+      <c r="N779" s="9">
+        <v>67.542213883677292</v>
+      </c>
+      <c r="S779" s="11"/>
+      <c r="V779" s="9"/>
+      <c r="W779" s="10"/>
+    </row>
+    <row r="780" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A780" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B780" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C780" s="9">
+        <v>70.973451327433622</v>
+      </c>
+      <c r="D780" s="9">
+        <v>77.00934579439253</v>
+      </c>
+      <c r="E780" t="s">
+        <v>11</v>
+      </c>
+      <c r="F780" s="10">
+        <v>565</v>
+      </c>
+      <c r="G780" s="10">
+        <v>538</v>
+      </c>
+      <c r="K780" s="9"/>
+      <c r="M780" s="9">
+        <v>70.973451327433622</v>
+      </c>
+      <c r="N780" s="9">
+        <v>77.00934579439253</v>
+      </c>
+      <c r="S780" s="11"/>
+      <c r="V780" s="9"/>
+      <c r="W780" s="10"/>
+    </row>
+    <row r="781" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A781" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B781" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C781" s="9">
+        <v>93.140794223826717</v>
+      </c>
+      <c r="D781" s="9">
+        <v>81.882770870337481</v>
+      </c>
+      <c r="E781" t="s">
+        <v>4</v>
+      </c>
+      <c r="F781" s="10">
+        <v>554</v>
+      </c>
+      <c r="G781" s="10">
+        <v>563</v>
+      </c>
+      <c r="K781" s="9"/>
+      <c r="M781" s="9">
+        <v>93.140794223826717</v>
+      </c>
+      <c r="N781" s="9">
+        <v>81.882770870337481</v>
+      </c>
+      <c r="S781" s="11"/>
+      <c r="V781" s="9"/>
+      <c r="W781" s="10"/>
+    </row>
+    <row r="782" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A782" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B782" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C782" s="9">
+        <v>88.948306595365423</v>
+      </c>
+      <c r="D782" s="9">
+        <v>75.044247787610615</v>
+      </c>
+      <c r="E782" t="s">
+        <v>5</v>
+      </c>
+      <c r="F782" s="10">
+        <v>561</v>
+      </c>
+      <c r="G782" s="10">
+        <v>565</v>
+      </c>
+      <c r="K782" s="9"/>
+      <c r="M782" s="9">
+        <v>88.948306595365423</v>
+      </c>
+      <c r="N782" s="9">
+        <v>75.044247787610615</v>
+      </c>
+      <c r="S782" s="11"/>
+      <c r="V782" s="9"/>
+      <c r="W782" s="10"/>
+    </row>
+    <row r="783" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A783" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B783" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C783" s="9">
+        <v>91.134751773049643</v>
+      </c>
+      <c r="D783" s="9">
+        <v>84.219858156028366</v>
+      </c>
+      <c r="E783" t="s">
+        <v>6</v>
+      </c>
+      <c r="F783" s="10">
+        <v>564</v>
+      </c>
+      <c r="G783" s="10">
+        <v>567</v>
+      </c>
+      <c r="K783" s="9"/>
+      <c r="M783" s="9">
+        <v>91.134751773049643</v>
+      </c>
+      <c r="N783" s="9">
+        <v>84.219858156028366</v>
+      </c>
+      <c r="S783" s="11"/>
+      <c r="V783" s="9"/>
+      <c r="W783" s="10"/>
+    </row>
+    <row r="784" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A784" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B784" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C784" s="9">
+        <v>90.172413793103445</v>
+      </c>
+      <c r="D784" s="9">
+        <v>77.777777777777786</v>
+      </c>
+      <c r="E784" t="s">
+        <v>7</v>
+      </c>
+      <c r="F784" s="10">
+        <v>580</v>
+      </c>
+      <c r="G784" s="10">
+        <v>585</v>
+      </c>
+      <c r="K784" s="9"/>
+      <c r="M784" s="9">
+        <v>90.172413793103445</v>
+      </c>
+      <c r="N784" s="9">
+        <v>77.777777777777786</v>
+      </c>
+      <c r="S784" s="11"/>
+      <c r="V784" s="9"/>
+      <c r="W784" s="10"/>
+    </row>
+    <row r="785" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A785" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B785" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C785" s="9">
+        <v>88.448275862068968</v>
+      </c>
+      <c r="D785" s="9">
+        <v>78.803418803418808</v>
+      </c>
+      <c r="E785" t="s">
+        <v>8</v>
+      </c>
+      <c r="F785" s="10">
+        <v>580</v>
+      </c>
+      <c r="G785" s="10">
+        <v>585</v>
+      </c>
+      <c r="K785" s="9"/>
+      <c r="M785" s="9">
+        <v>88.448275862068968</v>
+      </c>
+      <c r="N785" s="9">
+        <v>78.803418803418808</v>
+      </c>
+      <c r="S785" s="11"/>
+      <c r="V785" s="9"/>
+      <c r="W785" s="10"/>
+    </row>
+    <row r="786" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A786" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B786" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C786" s="9">
+        <v>86.206896551724128</v>
+      </c>
+      <c r="D786" s="9">
+        <v>81.538461538461533</v>
+      </c>
+      <c r="E786" t="s">
+        <v>40</v>
+      </c>
+      <c r="F786" s="10">
+        <v>580</v>
+      </c>
+      <c r="G786" s="10">
+        <v>585</v>
+      </c>
+      <c r="K786" s="9"/>
+      <c r="M786" s="9">
+        <v>86.206896551724128</v>
+      </c>
+      <c r="N786" s="9">
+        <v>81.538461538461533</v>
+      </c>
+      <c r="S786" s="11"/>
+      <c r="V786" s="9"/>
+      <c r="W786" s="10"/>
+    </row>
+    <row r="787" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A787" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B787" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C787" s="9">
+        <v>100</v>
+      </c>
+      <c r="D787" s="9">
+        <v>83.67697594501719</v>
+      </c>
+      <c r="E787" t="s">
+        <v>9</v>
+      </c>
+      <c r="F787" s="10">
+        <v>581</v>
+      </c>
+      <c r="G787" s="10">
+        <v>585</v>
+      </c>
       <c r="I787" s="9"/>
       <c r="J787" s="10"/>
-      <c r="R787" s="11"/>
-      <c r="U787" s="9"/>
-      <c r="V787" s="10"/>
-    </row>
-    <row r="788" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F788" s="11"/>
+      <c r="M787" s="9">
+        <v>100</v>
+      </c>
+      <c r="N787" s="9">
+        <v>83.67697594501719</v>
+      </c>
+      <c r="S787" s="11"/>
+      <c r="V787" s="9"/>
+      <c r="W787" s="10"/>
+    </row>
+    <row r="788" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A788" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B788" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C788" s="9">
+        <v>90.070921985815602</v>
+      </c>
+      <c r="D788" s="9">
+        <v>78.383128295254835</v>
+      </c>
+      <c r="E788" t="s">
+        <v>10</v>
+      </c>
+      <c r="F788" s="10">
+        <v>564</v>
+      </c>
+      <c r="G788" s="10">
+        <v>569</v>
+      </c>
       <c r="I788" s="9"/>
       <c r="J788" s="10"/>
-      <c r="R788" s="11"/>
-      <c r="U788" s="9"/>
-      <c r="V788" s="10"/>
-    </row>
-    <row r="789" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F789" s="11"/>
+      <c r="M788" s="9">
+        <v>90.070921985815602</v>
+      </c>
+      <c r="N788" s="9">
+        <v>78.383128295254835</v>
+      </c>
+      <c r="S788" s="11"/>
+      <c r="V788" s="9"/>
+      <c r="W788" s="10"/>
+    </row>
+    <row r="789" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A789" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B789" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C789" s="9">
+        <v>87.388987566607454</v>
+      </c>
+      <c r="D789" s="9">
+        <v>81.019332161687174</v>
+      </c>
+      <c r="E789" t="s">
+        <v>11</v>
+      </c>
+      <c r="F789" s="10">
+        <v>564</v>
+      </c>
+      <c r="G789" s="10">
+        <v>569</v>
+      </c>
       <c r="I789" s="9"/>
       <c r="J789" s="10"/>
-      <c r="R789" s="11"/>
-      <c r="U789" s="9"/>
-      <c r="V789" s="10"/>
-    </row>
-    <row r="790" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F790" s="11"/>
+      <c r="M789" s="9">
+        <v>87.388987566607454</v>
+      </c>
+      <c r="N789" s="9">
+        <v>81.019332161687174</v>
+      </c>
+      <c r="S789" s="11"/>
+      <c r="V789" s="9"/>
+      <c r="W789" s="10"/>
+    </row>
+    <row r="790" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A790" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B790" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C790" s="9">
+        <v>93.811074918566774</v>
+      </c>
+      <c r="D790" s="9">
+        <v>84.615384615384613</v>
+      </c>
+      <c r="E790" t="s">
+        <v>4</v>
+      </c>
+      <c r="F790" s="10">
+        <v>614</v>
+      </c>
+      <c r="G790" s="10">
+        <v>611</v>
+      </c>
       <c r="I790" s="9"/>
       <c r="J790" s="10"/>
-      <c r="R790" s="11"/>
-      <c r="U790" s="9"/>
-      <c r="V790" s="10"/>
-    </row>
-    <row r="791" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F791" s="11"/>
+      <c r="M790" s="9">
+        <v>93.811074918566774</v>
+      </c>
+      <c r="N790" s="9">
+        <v>84.615384615384613</v>
+      </c>
+      <c r="S790" s="11"/>
+      <c r="V790" s="9"/>
+      <c r="W790" s="10"/>
+    </row>
+    <row r="791" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A791" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B791" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C791" s="9">
+        <v>90.291262135922338</v>
+      </c>
+      <c r="D791" s="9">
+        <v>77.250409165302784</v>
+      </c>
+      <c r="E791" t="s">
+        <v>5</v>
+      </c>
+      <c r="F791" s="10">
+        <v>618</v>
+      </c>
+      <c r="G791" s="10">
+        <v>612</v>
+      </c>
       <c r="I791" s="9"/>
       <c r="J791" s="10"/>
-      <c r="R791" s="11"/>
-      <c r="U791" s="9"/>
-      <c r="V791" s="10"/>
-    </row>
-    <row r="792" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F792" s="11"/>
+      <c r="M791" s="9">
+        <v>90.291262135922338</v>
+      </c>
+      <c r="N791" s="9">
+        <v>77.250409165302784</v>
+      </c>
+      <c r="S791" s="11"/>
+      <c r="V791" s="9"/>
+      <c r="W791" s="10"/>
+    </row>
+    <row r="792" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A792" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B792" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C792" s="9">
+        <v>90.145395799676891</v>
+      </c>
+      <c r="D792" s="9">
+        <v>85.761047463175117</v>
+      </c>
+      <c r="E792" t="s">
+        <v>6</v>
+      </c>
+      <c r="F792" s="10">
+        <v>619</v>
+      </c>
+      <c r="G792" s="10">
+        <v>613</v>
+      </c>
       <c r="I792" s="9"/>
       <c r="J792" s="10"/>
-      <c r="R792" s="11"/>
-      <c r="U792" s="9"/>
-      <c r="V792" s="10"/>
-    </row>
-    <row r="793" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F793" s="11"/>
+      <c r="M792" s="9">
+        <v>90.145395799676891</v>
+      </c>
+      <c r="N792" s="9">
+        <v>85.761047463175117</v>
+      </c>
+      <c r="S792" s="11"/>
+      <c r="V792" s="9"/>
+      <c r="W792" s="10"/>
+    </row>
+    <row r="793" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A793" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B793" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C793" s="9">
+        <v>90.266875981161704</v>
+      </c>
+      <c r="D793" s="9">
+        <v>94.444444444444443</v>
+      </c>
+      <c r="E793" t="s">
+        <v>7</v>
+      </c>
+      <c r="F793" s="10">
+        <v>637</v>
+      </c>
+      <c r="G793" s="10">
+        <v>631</v>
+      </c>
       <c r="I793" s="9"/>
       <c r="J793" s="10"/>
-      <c r="R793" s="11"/>
-      <c r="U793" s="9"/>
-      <c r="V793" s="10"/>
-    </row>
-    <row r="794" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F794" s="11"/>
+      <c r="M793" s="9">
+        <v>90.266875981161704</v>
+      </c>
+      <c r="N793" s="9">
+        <v>94.444444444444443</v>
+      </c>
+      <c r="S793" s="11"/>
+      <c r="V793" s="9"/>
+      <c r="W793" s="10"/>
+    </row>
+    <row r="794" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A794" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B794" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C794" s="9">
+        <v>87.912087912087912</v>
+      </c>
+      <c r="D794" s="9">
+        <v>78.922345483359749</v>
+      </c>
+      <c r="E794" t="s">
+        <v>8</v>
+      </c>
+      <c r="F794" s="10">
+        <v>637</v>
+      </c>
+      <c r="G794" s="10">
+        <v>631</v>
+      </c>
       <c r="I794" s="9"/>
       <c r="J794" s="10"/>
-      <c r="R794" s="11"/>
-      <c r="U794" s="9"/>
-      <c r="V794" s="10"/>
-    </row>
-    <row r="795" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="R795" s="11"/>
-      <c r="U795" s="9"/>
-      <c r="V795" s="10"/>
-    </row>
-    <row r="796" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="R796" s="11"/>
-      <c r="U796" s="9"/>
-      <c r="V796" s="10"/>
-    </row>
-    <row r="797" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="R797" s="11"/>
-      <c r="U797" s="9"/>
-      <c r="V797" s="10"/>
-    </row>
-    <row r="798" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="R798" s="11"/>
-      <c r="U798" s="9"/>
-      <c r="V798" s="10"/>
-    </row>
-    <row r="799" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="R799" s="11"/>
-      <c r="U799" s="9"/>
-      <c r="V799" s="10"/>
-    </row>
-    <row r="800" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="R800" s="11"/>
-      <c r="U800" s="9"/>
-      <c r="V800" s="10"/>
-    </row>
-    <row r="801" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R801" s="11"/>
-      <c r="U801" s="9"/>
-      <c r="V801" s="10"/>
-    </row>
-    <row r="802" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R802" s="11"/>
-      <c r="U802" s="9"/>
-      <c r="V802" s="10"/>
-    </row>
-    <row r="803" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R803" s="11"/>
-      <c r="U803" s="9"/>
-      <c r="V803" s="10"/>
-    </row>
-    <row r="804" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R804" s="11"/>
-      <c r="U804" s="9"/>
-      <c r="V804" s="10"/>
-    </row>
-    <row r="805" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R805" s="11"/>
-      <c r="U805" s="9"/>
-      <c r="V805" s="10"/>
-    </row>
-    <row r="806" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R806" s="11"/>
-      <c r="U806" s="9"/>
-      <c r="V806" s="10"/>
-    </row>
-    <row r="807" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R807" s="11"/>
-      <c r="U807" s="9"/>
-      <c r="V807" s="10"/>
-    </row>
-    <row r="808" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R808" s="11"/>
-      <c r="U808" s="9"/>
-      <c r="V808" s="10"/>
-    </row>
-    <row r="809" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R809" s="11"/>
-      <c r="U809" s="9"/>
-      <c r="V809" s="10"/>
-    </row>
-    <row r="810" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R810" s="11"/>
-      <c r="U810" s="9"/>
-      <c r="V810" s="10"/>
-    </row>
-    <row r="811" spans="18:22" x14ac:dyDescent="0.25">
-      <c r="R811" s="11"/>
-      <c r="U811" s="9"/>
-      <c r="V811" s="10"/>
+      <c r="M794" s="9">
+        <v>87.912087912087912</v>
+      </c>
+      <c r="N794" s="9">
+        <v>78.922345483359749</v>
+      </c>
+      <c r="S794" s="11"/>
+      <c r="V794" s="9"/>
+      <c r="W794" s="10"/>
+    </row>
+    <row r="795" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A795" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B795" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C795" s="9">
+        <v>84.144427001569852</v>
+      </c>
+      <c r="D795" s="9">
+        <v>79.873217115689371</v>
+      </c>
+      <c r="E795" t="s">
+        <v>40</v>
+      </c>
+      <c r="F795" s="10">
+        <v>637</v>
+      </c>
+      <c r="G795" s="10">
+        <v>631</v>
+      </c>
+      <c r="M795" s="9">
+        <v>84.144427001569852</v>
+      </c>
+      <c r="N795" s="9">
+        <v>79.873217115689371</v>
+      </c>
+      <c r="S795" s="11"/>
+      <c r="V795" s="9"/>
+      <c r="W795" s="10"/>
+    </row>
+    <row r="796" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A796" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B796" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C796" s="9">
+        <v>94.444444444444443</v>
+      </c>
+      <c r="D796" s="9">
+        <v>80.66561014263074</v>
+      </c>
+      <c r="E796" t="s">
+        <v>9</v>
+      </c>
+      <c r="F796" s="10">
+        <v>637</v>
+      </c>
+      <c r="G796" s="10">
+        <v>631</v>
+      </c>
+      <c r="M796" s="9">
+        <v>94.444444444444443</v>
+      </c>
+      <c r="N796" s="9">
+        <v>80.66561014263074</v>
+      </c>
+      <c r="S796" s="11"/>
+      <c r="V796" s="9"/>
+      <c r="W796" s="10"/>
+    </row>
+    <row r="797" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A797" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B797" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C797" s="9">
+        <v>90.081300813008141</v>
+      </c>
+      <c r="D797" s="9">
+        <v>75.041050903119867</v>
+      </c>
+      <c r="E797" t="s">
+        <v>10</v>
+      </c>
+      <c r="F797" s="10">
+        <v>615</v>
+      </c>
+      <c r="G797" s="10">
+        <v>610</v>
+      </c>
+      <c r="M797" s="9">
+        <v>90.081300813008141</v>
+      </c>
+      <c r="N797" s="9">
+        <v>75.041050903119867</v>
+      </c>
+      <c r="S797" s="11"/>
+      <c r="V797" s="9"/>
+      <c r="W797" s="10"/>
+    </row>
+    <row r="798" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A798" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B798" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C798" s="9">
+        <v>86.591276252019384</v>
+      </c>
+      <c r="D798" s="9">
+        <v>78.559738134206228</v>
+      </c>
+      <c r="E798" t="s">
+        <v>11</v>
+      </c>
+      <c r="F798" s="10">
+        <v>619</v>
+      </c>
+      <c r="G798" s="10">
+        <v>614</v>
+      </c>
+      <c r="M798" s="9">
+        <v>86.591276252019384</v>
+      </c>
+      <c r="N798" s="9">
+        <v>78.559738134206228</v>
+      </c>
+      <c r="S798" s="11"/>
+      <c r="V798" s="9"/>
+      <c r="W798" s="10"/>
+    </row>
+    <row r="799" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A799" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B799" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C799" s="9">
+        <v>93.591654247391958</v>
+      </c>
+      <c r="D799" s="9">
+        <v>79.259259259259267</v>
+      </c>
+      <c r="E799" t="s">
+        <v>4</v>
+      </c>
+      <c r="F799" s="10">
+        <v>671</v>
+      </c>
+      <c r="G799" s="10">
+        <v>675</v>
+      </c>
+      <c r="M799" s="9">
+        <v>93.591654247391958</v>
+      </c>
+      <c r="N799" s="9">
+        <v>79.259259259259267</v>
+      </c>
+      <c r="S799" s="11"/>
+      <c r="V799" s="9"/>
+      <c r="W799" s="10"/>
+    </row>
+    <row r="800" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A800" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B800" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C800" s="9">
+        <v>89.280469897209997</v>
+      </c>
+      <c r="D800" s="9">
+        <v>71.216617210682486</v>
+      </c>
+      <c r="E800" t="s">
+        <v>5</v>
+      </c>
+      <c r="F800" s="10">
+        <v>681</v>
+      </c>
+      <c r="G800" s="10">
+        <v>679</v>
+      </c>
+      <c r="M800" s="9">
+        <v>89.280469897209997</v>
+      </c>
+      <c r="N800" s="9">
+        <v>71.216617210682486</v>
+      </c>
+      <c r="S800" s="11"/>
+      <c r="V800" s="9"/>
+      <c r="W800" s="10"/>
+    </row>
+    <row r="801" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A801" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B801" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C801" s="9">
+        <v>89.181286549707607</v>
+      </c>
+      <c r="D801" s="9">
+        <v>79.086892488954348</v>
+      </c>
+      <c r="E801" t="s">
+        <v>6</v>
+      </c>
+      <c r="F801" s="10">
+        <v>684</v>
+      </c>
+      <c r="G801" s="10">
+        <v>681</v>
+      </c>
+      <c r="M801" s="9">
+        <v>89.181286549707607</v>
+      </c>
+      <c r="N801" s="9">
+        <v>79.086892488954348</v>
+      </c>
+      <c r="S801" s="11"/>
+      <c r="V801" s="9"/>
+      <c r="W801" s="10"/>
+    </row>
+    <row r="802" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A802" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B802" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C802" s="9">
+        <v>89.787234042553195</v>
+      </c>
+      <c r="D802" s="9">
+        <v>95.454545454545453</v>
+      </c>
+      <c r="E802" t="s">
+        <v>7</v>
+      </c>
+      <c r="F802" s="10">
+        <v>706</v>
+      </c>
+      <c r="G802" s="10">
+        <v>703</v>
+      </c>
+      <c r="M802" s="9">
+        <v>89.787234042553195</v>
+      </c>
+      <c r="N802" s="9">
+        <v>95.454545454545453</v>
+      </c>
+      <c r="S802" s="11"/>
+      <c r="V802" s="9"/>
+      <c r="W802" s="10"/>
+    </row>
+    <row r="803" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A803" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B803" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C803" s="9">
+        <v>87.801418439716315</v>
+      </c>
+      <c r="D803" s="9">
+        <v>77.098150782361301</v>
+      </c>
+      <c r="E803" t="s">
+        <v>8</v>
+      </c>
+      <c r="F803" s="10">
+        <v>706</v>
+      </c>
+      <c r="G803" s="10">
+        <v>703</v>
+      </c>
+      <c r="M803" s="9">
+        <v>87.801418439716315</v>
+      </c>
+      <c r="N803" s="9">
+        <v>77.098150782361301</v>
+      </c>
+      <c r="S803" s="11"/>
+      <c r="V803" s="9"/>
+      <c r="W803" s="10"/>
+    </row>
+    <row r="804" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A804" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B804" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C804" s="9">
+        <v>85.835694050991492</v>
+      </c>
+      <c r="D804" s="9">
+        <v>80.085348506401147</v>
+      </c>
+      <c r="E804" t="s">
+        <v>40</v>
+      </c>
+      <c r="F804" s="10">
+        <v>706</v>
+      </c>
+      <c r="G804" s="10">
+        <v>703</v>
+      </c>
+      <c r="M804" s="9">
+        <v>85.835694050991492</v>
+      </c>
+      <c r="N804" s="9">
+        <v>80.085348506401147</v>
+      </c>
+      <c r="S804" s="11"/>
+      <c r="V804" s="9"/>
+      <c r="W804" s="10"/>
+    </row>
+    <row r="805" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A805" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B805" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C805" s="9">
+        <v>100</v>
+      </c>
+      <c r="D805" s="9">
+        <v>81.623931623931625</v>
+      </c>
+      <c r="E805" t="s">
+        <v>9</v>
+      </c>
+      <c r="F805" s="10">
+        <v>706</v>
+      </c>
+      <c r="G805" s="10">
+        <v>703</v>
+      </c>
+      <c r="M805" s="9">
+        <v>100</v>
+      </c>
+      <c r="N805" s="9">
+        <v>81.623931623931625</v>
+      </c>
+      <c r="S805" s="11"/>
+      <c r="V805" s="9"/>
+      <c r="W805" s="10"/>
+    </row>
+    <row r="806" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A806" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B806" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C806" s="9">
+        <v>89.473684210526315</v>
+      </c>
+      <c r="D806" s="9">
+        <v>71.365638766519822</v>
+      </c>
+      <c r="E806" t="s">
+        <v>10</v>
+      </c>
+      <c r="F806" s="10">
+        <v>684</v>
+      </c>
+      <c r="G806" s="10">
+        <v>681</v>
+      </c>
+      <c r="M806" s="9">
+        <v>89.473684210526315</v>
+      </c>
+      <c r="N806" s="9">
+        <v>71.365638766519822</v>
+      </c>
+      <c r="S806" s="11"/>
+      <c r="V806" s="9"/>
+      <c r="W806" s="10"/>
+    </row>
+    <row r="807" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A807" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B807" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C807" s="9">
+        <v>87.134502923976612</v>
+      </c>
+      <c r="D807" s="9">
+        <v>72.834067547723933</v>
+      </c>
+      <c r="E807" t="s">
+        <v>11</v>
+      </c>
+      <c r="F807" s="10">
+        <v>684</v>
+      </c>
+      <c r="G807" s="10">
+        <v>681</v>
+      </c>
+      <c r="M807" s="9">
+        <v>87.134502923976612</v>
+      </c>
+      <c r="N807" s="9">
+        <v>72.834067547723933</v>
+      </c>
+      <c r="S807" s="11"/>
+      <c r="V807" s="9"/>
+      <c r="W807" s="10"/>
+    </row>
+    <row r="808" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A808" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B808" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C808" s="9">
+        <v>91.623036649214669</v>
+      </c>
+      <c r="D808" s="9">
+        <v>73.480662983425418</v>
+      </c>
+      <c r="E808" t="s">
+        <v>4</v>
+      </c>
+      <c r="F808" s="10">
+        <v>191</v>
+      </c>
+      <c r="G808" s="10">
+        <v>181</v>
+      </c>
+      <c r="M808" s="9">
+        <v>91.623036649214669</v>
+      </c>
+      <c r="N808" s="9">
+        <v>73.480662983425418</v>
+      </c>
+      <c r="S808" s="11"/>
+      <c r="V808" s="9"/>
+      <c r="W808" s="10"/>
+    </row>
+    <row r="809" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A809" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B809" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C809" s="9">
+        <v>87.434554973821989</v>
+      </c>
+      <c r="D809" s="9">
+        <v>63.186813186813183</v>
+      </c>
+      <c r="E809" t="s">
+        <v>5</v>
+      </c>
+      <c r="F809" s="10">
+        <v>191</v>
+      </c>
+      <c r="G809" s="10">
+        <v>182</v>
+      </c>
+      <c r="M809" s="9">
+        <v>87.434554973821989</v>
+      </c>
+      <c r="N809" s="9">
+        <v>63.186813186813183</v>
+      </c>
+      <c r="S809" s="11"/>
+      <c r="V809" s="9"/>
+      <c r="W809" s="10"/>
+    </row>
+    <row r="810" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A810" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B810" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C810" s="9">
+        <v>89.005235602094231</v>
+      </c>
+      <c r="D810" s="9">
+        <v>67.032967032967036</v>
+      </c>
+      <c r="E810" t="s">
+        <v>6</v>
+      </c>
+      <c r="F810" s="10">
+        <v>191</v>
+      </c>
+      <c r="G810" s="10">
+        <v>182</v>
+      </c>
+      <c r="M810" s="9">
+        <v>89.005235602094231</v>
+      </c>
+      <c r="N810" s="9">
+        <v>67.032967032967036</v>
+      </c>
+      <c r="S810" s="11"/>
+      <c r="V810" s="9"/>
+      <c r="W810" s="10"/>
+    </row>
+    <row r="811" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A811" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B811" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C811" s="9">
+        <v>91.959798994974875</v>
+      </c>
+      <c r="D811" s="9">
+        <v>100</v>
+      </c>
+      <c r="E811" t="s">
+        <v>7</v>
+      </c>
+      <c r="F811" s="10">
+        <v>199</v>
+      </c>
+      <c r="G811" s="10">
+        <v>191</v>
+      </c>
+      <c r="M811" s="9">
+        <v>91.959798994974875</v>
+      </c>
+      <c r="N811" s="9">
+        <v>100</v>
+      </c>
+      <c r="S811" s="11"/>
+      <c r="V811" s="9"/>
+      <c r="W811" s="10"/>
+    </row>
+    <row r="812" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A812" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B812" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C812" s="9">
+        <v>89.949748743718601</v>
+      </c>
+      <c r="D812" s="9">
+        <v>67.015706806282722</v>
+      </c>
+      <c r="E812" t="s">
+        <v>8</v>
+      </c>
+      <c r="F812" s="10">
+        <v>199</v>
+      </c>
+      <c r="G812" s="10">
+        <v>191</v>
+      </c>
+      <c r="M812" s="9">
+        <v>89.949748743718601</v>
+      </c>
+      <c r="N812" s="9">
+        <v>67.015706806282722</v>
+      </c>
+      <c r="S812" s="11"/>
+      <c r="V812" s="9"/>
+      <c r="W812" s="10"/>
+    </row>
+    <row r="813" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A813" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B813" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C813" s="9">
+        <v>91.959798994974875</v>
+      </c>
+      <c r="D813" s="9">
+        <v>70.680628272251312</v>
+      </c>
+      <c r="E813" t="s">
+        <v>40</v>
+      </c>
+      <c r="F813" s="10">
+        <v>199</v>
+      </c>
+      <c r="G813" s="10">
+        <v>191</v>
+      </c>
+      <c r="M813" s="9">
+        <v>91.959798994974875</v>
+      </c>
+      <c r="N813" s="9">
+        <v>70.680628272251312</v>
+      </c>
+      <c r="S813" s="11"/>
+      <c r="V813" s="9"/>
+      <c r="W813" s="10"/>
+    </row>
+    <row r="814" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A814" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B814" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C814" s="9">
+        <v>100</v>
+      </c>
+      <c r="D814" s="9">
+        <v>66.492146596858632</v>
+      </c>
+      <c r="E814" t="s">
+        <v>9</v>
+      </c>
+      <c r="F814" s="10">
+        <v>199</v>
+      </c>
+      <c r="G814" s="10">
+        <v>191</v>
+      </c>
+      <c r="M814" s="9">
+        <v>100</v>
+      </c>
+      <c r="N814" s="9">
+        <v>66.492146596858632</v>
+      </c>
+      <c r="S814" s="11"/>
+      <c r="V814" s="9"/>
+      <c r="W814" s="10"/>
+    </row>
+    <row r="815" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A815" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B815" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C815" s="9">
+        <v>73.298429319371721</v>
+      </c>
+      <c r="D815" s="9">
+        <v>61.202185792349731</v>
+      </c>
+      <c r="E815" t="s">
+        <v>10</v>
+      </c>
+      <c r="F815" s="10">
+        <v>191</v>
+      </c>
+      <c r="G815" s="10">
+        <v>183</v>
+      </c>
+      <c r="M815" s="9">
+        <v>73.298429319371721</v>
+      </c>
+      <c r="N815" s="9">
+        <v>61.202185792349731</v>
+      </c>
+      <c r="S815" s="11"/>
+      <c r="V815" s="9"/>
+      <c r="W815" s="10"/>
+    </row>
+    <row r="816" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A816" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B816" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C816" s="9">
+        <v>65.968586387434542</v>
+      </c>
+      <c r="D816" s="9">
+        <v>62.295081967213115</v>
+      </c>
+      <c r="E816" t="s">
+        <v>11</v>
+      </c>
+      <c r="F816" s="10">
+        <v>191</v>
+      </c>
+      <c r="G816" s="10">
+        <v>183</v>
+      </c>
+      <c r="M816" s="9">
+        <v>65.968586387434542</v>
+      </c>
+      <c r="N816" s="9">
+        <v>62.295081967213115</v>
+      </c>
+      <c r="S816" s="11"/>
+      <c r="V816" s="9"/>
+      <c r="W816" s="10"/>
+    </row>
+    <row r="817" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S817" s="11"/>
+      <c r="V817" s="9"/>
+      <c r="W817" s="10"/>
+    </row>
+    <row r="818" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S818" s="11"/>
+      <c r="V818" s="9"/>
+      <c r="W818" s="10"/>
+    </row>
+    <row r="819" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S819" s="11"/>
+      <c r="V819" s="9"/>
+      <c r="W819" s="10"/>
+    </row>
+    <row r="820" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S820" s="11"/>
+      <c r="V820" s="9"/>
+      <c r="W820" s="10"/>
+    </row>
+    <row r="821" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S821" s="11"/>
+      <c r="V821" s="9"/>
+      <c r="W821" s="10"/>
+    </row>
+    <row r="822" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S822" s="11"/>
+      <c r="V822" s="9"/>
+      <c r="W822" s="10"/>
+    </row>
+    <row r="823" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S823" s="11"/>
+      <c r="V823" s="9"/>
+      <c r="W823" s="10"/>
+    </row>
+    <row r="824" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S824" s="11"/>
+      <c r="V824" s="9"/>
+      <c r="W824" s="10"/>
+    </row>
+    <row r="825" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S825" s="11"/>
+      <c r="V825" s="9"/>
+      <c r="W825" s="10"/>
+    </row>
+    <row r="826" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S826" s="11"/>
+      <c r="V826" s="9"/>
+      <c r="W826" s="10"/>
+    </row>
+    <row r="827" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S827" s="11"/>
+      <c r="V827" s="9"/>
+      <c r="W827" s="10"/>
+    </row>
+    <row r="828" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S828" s="11"/>
+      <c r="V828" s="9"/>
+      <c r="W828" s="10"/>
+    </row>
+    <row r="829" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S829" s="11"/>
+      <c r="V829" s="9"/>
+      <c r="W829" s="10"/>
+    </row>
+    <row r="830" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S830" s="11"/>
+      <c r="V830" s="9"/>
+      <c r="W830" s="10"/>
+    </row>
+    <row r="831" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S831" s="11"/>
+      <c r="V831" s="9"/>
+      <c r="W831" s="10"/>
+    </row>
+    <row r="832" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S832" s="11"/>
+      <c r="V832" s="9"/>
+      <c r="W832" s="10"/>
+    </row>
+    <row r="833" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S833" s="11"/>
+      <c r="V833" s="9"/>
+      <c r="W833" s="10"/>
+    </row>
+    <row r="834" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S834" s="11"/>
+      <c r="V834" s="9"/>
+      <c r="W834" s="10"/>
+    </row>
+    <row r="835" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S835" s="11"/>
+      <c r="V835" s="9"/>
+      <c r="W835" s="10"/>
+    </row>
+    <row r="836" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S836" s="11"/>
+      <c r="V836" s="9"/>
+      <c r="W836" s="10"/>
+    </row>
+    <row r="837" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S837" s="11"/>
+      <c r="V837" s="9"/>
+      <c r="W837" s="10"/>
+    </row>
+    <row r="838" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S838" s="11"/>
+      <c r="V838" s="9"/>
+      <c r="W838" s="10"/>
+    </row>
+    <row r="839" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S839" s="11"/>
+      <c r="V839" s="9"/>
+      <c r="W839" s="10"/>
+    </row>
+    <row r="840" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S840" s="11"/>
+      <c r="V840" s="9"/>
+      <c r="W840" s="10"/>
+    </row>
+    <row r="841" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S841" s="11"/>
+      <c r="V841" s="9"/>
+      <c r="W841" s="10"/>
+    </row>
+    <row r="842" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S842" s="11"/>
+      <c r="V842" s="9"/>
+      <c r="W842" s="10"/>
+    </row>
+    <row r="843" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S843" s="11"/>
+      <c r="V843" s="9"/>
+      <c r="W843" s="10"/>
+    </row>
+    <row r="844" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S844" s="11"/>
+      <c r="V844" s="9"/>
+      <c r="W844" s="10"/>
+    </row>
+    <row r="845" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S845" s="11"/>
+      <c r="V845" s="9"/>
+      <c r="W845" s="10"/>
+    </row>
+    <row r="846" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S846" s="11"/>
+      <c r="V846" s="9"/>
+      <c r="W846" s="10"/>
+    </row>
+    <row r="847" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S847" s="11"/>
+      <c r="V847" s="9"/>
+      <c r="W847" s="10"/>
+    </row>
+    <row r="848" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S848" s="11"/>
+      <c r="V848" s="9"/>
+      <c r="W848" s="10"/>
+    </row>
+    <row r="849" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S849" s="11"/>
+      <c r="V849" s="9"/>
+      <c r="W849" s="10"/>
+    </row>
+    <row r="850" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S850" s="11"/>
+      <c r="V850" s="9"/>
+      <c r="W850" s="10"/>
+    </row>
+    <row r="851" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S851" s="11"/>
+      <c r="V851" s="9"/>
+      <c r="W851" s="10"/>
+    </row>
+    <row r="852" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S852" s="11"/>
+      <c r="V852" s="9"/>
+      <c r="W852" s="10"/>
+    </row>
+    <row r="853" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S853" s="11"/>
+      <c r="V853" s="9"/>
+      <c r="W853" s="10"/>
+    </row>
+    <row r="854" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S854" s="11"/>
+      <c r="V854" s="9"/>
+      <c r="W854" s="10"/>
+    </row>
+    <row r="855" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S855" s="11"/>
+      <c r="V855" s="9"/>
+      <c r="W855" s="10"/>
+    </row>
+    <row r="856" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S856" s="11"/>
+      <c r="V856" s="9"/>
+      <c r="W856" s="10"/>
+    </row>
+    <row r="857" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S857" s="11"/>
+      <c r="V857" s="9"/>
+      <c r="W857" s="10"/>
+    </row>
+    <row r="858" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S858" s="11"/>
+      <c r="V858" s="9"/>
+      <c r="W858" s="10"/>
+    </row>
+    <row r="859" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S859" s="11"/>
+      <c r="V859" s="9"/>
+      <c r="W859" s="10"/>
+    </row>
+    <row r="860" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S860" s="11"/>
+      <c r="V860" s="9"/>
+      <c r="W860" s="10"/>
+    </row>
+    <row r="861" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S861" s="11"/>
+      <c r="V861" s="9"/>
+      <c r="W861" s="10"/>
+    </row>
+    <row r="862" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S862" s="11"/>
+      <c r="V862" s="9"/>
+      <c r="W862" s="10"/>
+    </row>
+    <row r="863" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S863" s="11"/>
+      <c r="V863" s="9"/>
+      <c r="W863" s="10"/>
+    </row>
+    <row r="864" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S864" s="11"/>
+      <c r="V864" s="9"/>
+      <c r="W864" s="10"/>
+    </row>
+    <row r="865" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S865" s="11"/>
+      <c r="V865" s="9"/>
+      <c r="W865" s="10"/>
+    </row>
+    <row r="866" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S866" s="11"/>
+      <c r="V866" s="9"/>
+      <c r="W866" s="10"/>
+    </row>
+    <row r="867" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S867" s="11"/>
+      <c r="V867" s="9"/>
+      <c r="W867" s="10"/>
+    </row>
+    <row r="868" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S868" s="11"/>
+      <c r="V868" s="9"/>
+      <c r="W868" s="10"/>
+    </row>
+    <row r="869" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S869" s="11"/>
+      <c r="V869" s="9"/>
+      <c r="W869" s="10"/>
+    </row>
+    <row r="870" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S870" s="11"/>
+      <c r="V870" s="9"/>
+      <c r="W870" s="10"/>
+    </row>
+    <row r="871" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S871" s="11"/>
+      <c r="V871" s="9"/>
+      <c r="W871" s="10"/>
+    </row>
+    <row r="872" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S872" s="11"/>
+      <c r="V872" s="9"/>
+      <c r="W872" s="10"/>
+    </row>
+    <row r="873" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S873" s="11"/>
+      <c r="V873" s="9"/>
+      <c r="W873" s="10"/>
+    </row>
+    <row r="874" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S874" s="11"/>
+      <c r="V874" s="9"/>
+      <c r="W874" s="10"/>
+    </row>
+    <row r="875" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S875" s="11"/>
+      <c r="V875" s="9"/>
+      <c r="W875" s="10"/>
+    </row>
+    <row r="876" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S876" s="11"/>
+      <c r="V876" s="9"/>
+      <c r="W876" s="10"/>
+    </row>
+    <row r="877" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S877" s="11"/>
+      <c r="V877" s="9"/>
+      <c r="W877" s="10"/>
+    </row>
+    <row r="878" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S878" s="11"/>
+      <c r="V878" s="9"/>
+      <c r="W878" s="10"/>
+    </row>
+    <row r="879" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S879" s="11"/>
+      <c r="V879" s="9"/>
+      <c r="W879" s="10"/>
+    </row>
+    <row r="880" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S880" s="11"/>
+      <c r="V880" s="9"/>
+      <c r="W880" s="10"/>
+    </row>
+    <row r="881" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S881" s="11"/>
+      <c r="V881" s="9"/>
+      <c r="W881" s="10"/>
+    </row>
+    <row r="882" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S882" s="11"/>
+      <c r="V882" s="9"/>
+      <c r="W882" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="E1:E649" xr:uid="{83DB8626-0F1C-45B1-B742-083DABC571E5}"/>
@@ -34623,6 +36349,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A39:A50"/>
+    <mergeCell ref="A51:A62"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="A63:A74"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="A3:A14"/>
     <mergeCell ref="A15:A26"/>
@@ -34633,11 +36364,6 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A39:A50"/>
-    <mergeCell ref="A51:A62"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="A63:A74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34658,6 +36384,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="304c15a9-2ddf-417f-8912-8cf6a1609eab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001F0BB1C88B026E498516C75AD9D26285" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5fb15fa5fb8ec6c836b9d7d5a959bb8a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="304c15a9-2ddf-417f-8912-8cf6a1609eab" xmlns:ns3="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9ddd68b27bb9e6f16d84f1577050cb1c" ns2:_="" ns3:_="">
     <xsd:import namespace="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
@@ -34912,17 +36649,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="304c15a9-2ddf-417f-8912-8cf6a1609eab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7B921E6-00DE-4D0E-B400-431DDE188271}">
   <ds:schemaRefs>
@@ -34932,6 +36658,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11171811-4752-42CE-913B-A1196C5C2AA8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
+    <ds:schemaRef ds:uri="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BAB492D-29AE-4FBB-B174-1C81B2D3C817}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34948,15 +36685,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11171811-4752-42CE-913B-A1196C5C2AA8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
-    <ds:schemaRef ds:uri="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>